--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,6 +314,89 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0401200101</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VĨNH CHÂU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Số 7 Lỗ Giáng 3, Phường Hòa Xuân, TP Đà Nẵng, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>2.8703704E7</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>2296296.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>3.1E7</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,172 +314,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>C25THV</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>09/10/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>0401200101</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH VĨNH CHÂU</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Số 7 Lỗ Giáng 3, Phường Hòa Xuân, TP Đà Nẵng, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>2.8703704E7</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>2296296.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="n">
-        <v>3.1E7</v>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>C25THV</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>VNPT thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>125 Hai Bà Trưng, Phường Sài Gòn, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>1.8E7</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>1800000.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="n">
-        <v>1.98E7</v>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,6 +314,172 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0401200101</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VĨNH CHÂU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Số 7 Lỗ Giáng 3, Phường Hòa Xuân, TP Đà Nẵng, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>2.8703704E7</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>2296296.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>3.1E7</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>VNPT thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>125 Hai Bà Trưng, Phường Sài Gòn, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1.8E7</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,6 +314,172 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25TNT</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0303765858</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>36/21 Đường D2, Phường Thạnh Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3.4776E8</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>2.78208E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>3.755808E8</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25TNT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>0303765858</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>36/21 Đường D2, Phường 25, Quận Bình Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>3.0235E8</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>2.4188E7</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>3.26538E8</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,172 +314,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>C25TNT</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>28/10/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>0303765858</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>36/21 Đường D2, Phường Thạnh Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>3.4776E8</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>2.78208E7</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="n">
-        <v>3.755808E8</v>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>C25TNT</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>28/10/2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>0303765858</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>36/21 Đường D2, Phường 25, Quận Bình Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>3.0235E8</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>2.4188E7</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="n">
-        <v>3.26538E8</v>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/10/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/10/Hoadondientu.xlsx
@@ -314,6 +314,2982 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3501755776</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HẢI LƯU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 1, Số 155 Nguyễn Thái Học, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>5555556.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>444444.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>6000000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>3501890648</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN  GT LINE Á CHÂU</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Đường số 11 khu công nghiệp Đông Xuyên, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>563333.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>45067.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>608400.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>3501178180</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG MINH HÒA</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>48 Đặng Nguyên Cẩn, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>3611111.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>288889.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>3900000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>3502401089</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN GYRO PACIFIC</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>935/2 Bình Giã, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>3590000.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>287200.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>3877200.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3502557294</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIẢI TRÍ VÀ NGHỆ THUẬT HU BEACH</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Số 151 Thùy Vân, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>5.5830556E7</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>4466444.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>6.0297E7</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>0316029245</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TỔNG HỢP HOÀI NHƠN</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>1/1/1B5 Đường Linh Đông, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>2.907E7</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>2325600.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>3.13956E7</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3502283798</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG BÌNH AN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>12G1 Ngô Đức Kế, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>4.6537333E7</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>3722987.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>5.026032E7</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>3502283798</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG BÌNH AN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>12G1 Ngô Đức Kế, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>7.7537079E7</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>6202966.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>8.3740045E7</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3502545933</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG DƯƠNG TIẾN TÀI</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>79 Huyền Trân Công Chúa, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>9264400.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>741152.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1.0005552E7</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>0316758216</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KIẾN TRÚC - XÂY DỰNG KYOUDAI</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>73 Hoa Sữa, Phường Cầu Kiệu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>6553704.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>524296.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>7078000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>3500866723</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SX TM DV THÀNH ĐẠT</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>544B Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>2932407.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>234593.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>3167000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>3502239615</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN DỊCH VỤ DU LỊCH TUYẾT LAN</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Số 1A Phó Đức Chính, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>2970000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>237600.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>3207600.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Giang Thị Xuyên</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Số 30 Tiền Cảng, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1.35145E7</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1081160.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>1.459566E7</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>0306213397-001</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẦU TƯ PHÁT TRIỂN GIÁO DỤC HOÀNG VIỆT</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>17 Trương Vĩnh Ký, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>361111.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>28889.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>390000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>3501860185</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI XÂY DỰNG VIỆT PHÚ GIA</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Số 527D Bình Giã, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>653611.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>52289.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>705900.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>3500612824</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN LẠC VIỆT</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Số 159 - 163 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>1.026E7</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>820800.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>1.10808E7</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>3501178180</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG MINH HÒA</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>48 Đặng Nguyên Cẩn, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>4212963.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>337037.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>3502346007</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIẢI PHÁP NHÀ XANH</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Số 222 Huyền Trân Công Chúa, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>2.7895E7</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>2231600.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>3.01266E7</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>3500664773</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG ĐỨC TUẤN</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>558 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>3.1111112E7</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>2488889.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>3.3600001E7</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>3502314333</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>TRƯỜNG TIỂU HỌC, TRUNG HỌC CƠ SỞ VÀ TRUNG HỌC PHỔ THÔNG HỌC VIỆN ANH QUỐC</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>165 Nguyễn Hữu Thọ, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>5574074.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>445926.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>6020000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>3501178180</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG MINH HÒA</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>48 Đặng Nguyên Cẩn, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>3737306.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>298984.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4036290.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>3501755776</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HẢI LƯU</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 1, Số 155 đường Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>1166667.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>93333.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>1260000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>3500612824</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN LẠC VIỆT</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Số 159 - 163 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>2.0987037E7</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1678963.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>2.2666E7</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>3500354108-002</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>QUÁN ĂN GÀNH HÀO 2 - DNTN XĂNG DẦU LONG PHƯỚC</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Số 09 Hạ Long, Phường  Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>1.3273333E7</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>1061867.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>1.43352E7</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>3502105812</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THIẾT KẾ XÂY DỰNG KIẾN GIA VIỆT</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>3.2568519E7</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>2605482.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>3.5174001E7</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ THỦY</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>213/13 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>6.3021296E7</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>5041704.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>6.8063E7</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>3500442192</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ DA VÀNG</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Số 3 Hạ Long, Phường  Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>252407.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>20193.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>272600.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>3501492911</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG TOÀN ANH TÚ</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>18/5 Cô Bắc, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>2300000.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>184000.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>2484000.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>3500612824</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN LẠC VIỆT</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Số 159 - 163 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1.5226852E7</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1218148.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>1.6445E7</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>3500774663</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG ĐỨC TỈNH</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Bình Đức, Xã Ngãi Giao, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>9.75E7</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>7800000.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>1.053E8</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>3502417402</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TƯ VẤN XÂY DỰNG CÔNG DANH</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>16 Triệu Việt Vương, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>8735000.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>698800.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>9433800.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>3500102693</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DU LỊCH TÂN MÊ KÔNG</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Trần Hưng Đạo, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>5135000.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>410800.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>5545800.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>3501792288</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN PC AN KHANG</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Số 780/11/22 Bình Giã, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>9240000.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>739200.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>9979200.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>PHẠM THỊ LÝ</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Thửa đất số 181,Tờ bản đồ số 36, Hẻm 459, Đường Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>1.7392778E7</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>1391422.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>1.87842E7</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>3500612824</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN LẠC VIỆT</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Số 159 - 163 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>4837963.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>387037.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>5225000.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>3500664773</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG ĐỨC TUẤN</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>558 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>1.2833333E7</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1026667.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>1.386E7</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
